--- a/payment_forms/005_multiple_products_order_form--payment_forms.xlsx
+++ b/payment_forms/005_multiple_products_order_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -2027,12 +2027,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
@@ -2163,12 +2163,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -2197,12 +2197,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -2248,12 +2248,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -2265,12 +2265,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
@@ -2333,12 +2333,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -2367,12 +2367,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -2401,12 +2401,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -2469,12 +2469,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
@@ -2503,12 +2503,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -2571,12 +2571,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -2588,12 +2588,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -2605,12 +2605,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -2622,12 +2622,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
@@ -2673,12 +2673,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -2690,12 +2690,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -2724,12 +2724,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -2741,12 +2741,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -2758,12 +2758,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -2809,12 +2809,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
@@ -2843,12 +2843,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -2860,12 +2860,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -2911,12 +2911,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -2928,12 +2928,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -2945,12 +2945,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -2979,12 +2979,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -2996,12 +2996,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -3030,12 +3030,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -3081,12 +3081,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -3166,12 +3166,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
@@ -3183,12 +3183,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -3200,12 +3200,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -3217,12 +3217,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -3268,12 +3268,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -3302,12 +3302,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -3319,12 +3319,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -3336,12 +3336,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -3387,12 +3387,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -3421,12 +3421,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -3438,12 +3438,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -3455,12 +3455,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -3472,12 +3472,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
@@ -3523,12 +3523,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>{'value':_'product_1',_'label':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>{'value': 'product_1', 'label': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -3540,12 +3540,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>{'value':_'product_2',_'label':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>{'value': 'product_2', 'label': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -3557,12 +3557,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>{'value':_'product_3',_'label':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>{'value': 'product_3', 'label': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>{'value':_'product_4',_'label':_'product_4'}</t>
+          <t>product_4</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>{'value': 'product_4', 'label': 'Product 4'}</t>
+          <t>Product 4</t>
         </is>
       </c>
     </row>
@@ -3591,12 +3591,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>{'value':_'product_5',_'label':_'product_5'}</t>
+          <t>product_5</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>{'value': 'product_5', 'label': 'Product 5'}</t>
+          <t>Product 5</t>
         </is>
       </c>
     </row>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>{'value':_'product_6',_'label':_'product_6'}</t>
+          <t>product_6</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>{'value': 'product_6', 'label': 'Product 6'}</t>
+          <t>Product 6</t>
         </is>
       </c>
     </row>
@@ -3625,12 +3625,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>{'value':_'product_7',_'label':_'product_7'}</t>
+          <t>product_7</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>{'value': 'product_7', 'label': 'Product 7'}</t>
+          <t>Product 7</t>
         </is>
       </c>
     </row>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>{'value':_'product_8',_'label':_'product_8'}</t>
+          <t>product_8</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>{'value': 'product_8', 'label': 'Product 8'}</t>
+          <t>Product 8</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>{'value':_'product_9',_'label':_'product_9'}</t>
+          <t>product_9</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>{'value': 'product_9', 'label': 'Product 9'}</t>
+          <t>Product 9</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3676,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>{'value':_'product_10',_'label':_'product_10'}</t>
+          <t>product_10</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>{'value': 'product_10', 'label': 'Product 10'}</t>
+          <t>Product 10</t>
         </is>
       </c>
     </row>
